--- a/trening/navigator-narusheniya.xlsx
+++ b/trening/navigator-narusheniya.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -96,6 +96,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,16 +474,16 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>№</t>
         </is>
@@ -505,43 +514,39 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="96" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+    <row r="2" ht="142" customHeight="1">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Нарушения процесса по видео</t>
+          <t>Найди нарушения в процессе по видео</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Группа по раскадровке смены подрядчика ООО «СеверМонтаж» находит нарушения допуска, инструктажа, обучения и стажировки. Бытовые нарушения в кадры не заложены. Каждое замечание группа подтверждает пунктом стандарта. Перечень нарушений на этой вкладке не раскрывается.</t>
+          <t>Группа смотрит раскадровку работы подрядчика на площадке дочернего общества и фиксирует нарушения процесса допуска и обучения. На кадрах только работники подрядной организации: сотрудников ПАО «Газпром нефть» не показываем. Каждое нарушение группа подтверждает пунктом стандарта и записывает в бланк. В бланке остаются формулировка нарушения и ссылка на пункт, которым группа его подтвердила.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>М-16.01.10-14, разделы 4 и 5. Памятка участника. Матрица ответственности, блок инструктажей.</t>
+          <t>М-16.01.10-14, разделы 4 и 5. Матрица ответственности, блок инструктажей.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>uchastniku/01-video-narusheniya.md: раскадровка и бланк фиксации. Печатать по одному комплекту на группу.</t>
+          <t>Раскадровка видеокейса подрядчика. Бланк фиксации нарушений.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>М-16.01.10-14, раздел 4; раздел 5, пункты 5.1–5.8, в том числе 5.3.2 и 5.5.1. Сверка с Правилами № 2464, пункты 8–24 и 25–31, 86–90.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="96" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Раздел 4. Раздел 5 (п. 5.1–5.8), в том числе п. 5.3.2 и п. 5.5.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="142" customHeight="1">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -550,30 +555,28 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Группа заполняет матрицу на 10 должностей. В наборе обязательно есть руководители, специалисты и работники рабочих профессий. Для каждой должности указывают программы, место обучения, периодичность, минимум часов и необходимость стажировки. Разбор отдельных ошибок матрицы на этой вкладке не раскрывается.</t>
+          <t>Группа заполняет матрицу обучения на десять профессий с разными функциями. В наборе обязательно есть руководители, специалисты и работники рабочих профессий. Для каждой должности указывают программы «А», «Б», «В», «ОПП» и «СИЗ», место обучения — внутреннее или внешнее, периодичность и часы. Заполненную матрицу группа сверяет с таблицами стандарта и приложением 1.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>М-16.01.10-14, таблица 1 раздела 6.2 и таблица 2 раздела 6.5, приложение 1. Памятка участника. Условия кейса в карточке задания 2.</t>
+          <t>М-16.01.10-14, таблица 1 раздела 6.2 и таблица 2 раздела 6.5. Приложение 1. Матрица ответственности, операции 1–3 блока обучения.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>uchastniku/02-matrica-obuchenij.md: 10 карточек должностей и пустая матрица. По одному комплекту на группу.</t>
+          <t>10 карточек профессий. Пустая матрица обучения на группу.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>М-16.01.10-14, раздел 6.2 (таблица 1), раздел 6.4, раздел 6.5 (таблица 2), пункт 5.3.2, приложение 1. Сверка с Правилами № 2464, пункты 46, 53–55, 33–42.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="96" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>Раздел 6.2 (таблица 1). Раздел 6.4. Раздел 6.5 (таблица 2). П. 5.3.2. Приложение 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="126" customHeight="1">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -582,94 +585,88 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Группа разрезает карточки и раскладывает функции по ролям. Одна функция закрепляется за одной основной ролью, которая выполняет действие. Лишние действия откладывают отдельно. Подробная раскладка на этой вкладке не раскрывается.</t>
+          <t>Группа раскладывает карточки функций по ролям и определяет, кто выполняет, согласует, утверждает и контролирует каждое действие. Разбирают инструктаж, обучение, проверку знания и стажировку. Ориентир — матрица ответственности и разделы стандарта. В конце группа сверяет раскладку карточек с матрицей и оставляет согласованный вариант.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Матрица ответственности: блоки инструктажей, обучения и стажировки. М-16.01.10-14, раздел 4. Карточки ролей из задания 3.</t>
+          <t>Матрица ответственности, блоки инструктажей, обучения и стажировки. М-16.01.10-14, раздел 4.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>uchastniku/03-matrica-otvetstvennosti.md: 6 карточек ролей и карточки функций. Нарезать до занятия, один комплект на группу из 3 человек. Бланк раскладки.</t>
+          <t>Карточки ролей и карточки функций. Нарезать до занятия, один комплект на группу.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>М-16.01.10-14, раздел 5; разделы 6.4–6.8; разделы 7.2–7.5. Сверка с Правилами № 2464, пункты 10–22, 44, 72–77, 91–93.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="96" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Раздел 5. Разделы 6.4–6.8. Разделы 7.2–7.5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="126" customHeight="1">
+      <c r="A5" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Ошибки в программе обучения</t>
+          <t>Найди ошибки в программе обучения</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Группа читает учебную программу подрядчика и выписывает ошибки: лишние темы, ссылки на недействующие акты, неверные категории, часы, практика и периодичность. Сам перечень ошибок на этой вкладке не раскрывается.</t>
+          <t>Группа получает учебную программу без пометок и отмечает в ней ошибки. Ищут лишние темы, ссылки на недействующие нормативные акты, неверную категорию работников, а также неверные часы и место обучения. Каждое замечание записывают в бланк и подтверждают пунктом стандарта или шаблоном программы. Итог — заполненный бланк замечаний по программе.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>М-16.01.10-14, разделы 6.1–6.5, таблицы 1 и 2, библиография. Шаблоны программ Ш-16.01.10-05–31. Памятка участника.</t>
+          <t>М-16.01.10-14, таблицы 1 и 2, библиография, шаблоны Ш-16.01.10-05–31.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>uchastniku/04-programma-s-oshibkami.md: программа без пометок. Бланк замечаний ведут на обороте или отдельном листе.</t>
+          <t>Учебная программа с заложенными ошибками без пометок. Бланк для замечаний.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>М-16.01.10-14, разделы 6.1–6.3 и 6.5, введение и библиография. Сверка с Правилами № 2464, пункты 45–55.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="96" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>Разделы 6.1–6.3. Раздел 6.5. Введение и библиография.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="142" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Аудит допуска работника</t>
+          <t>Аудит допуска работника в части охраны труда</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Группа по учебному личному делу монтажника решает, можно ли допустить его к самостоятельной работе на высоте. В комплекте протоколы, выписки журналов и лист стажировки. Перечень нарушений на этой вкладке не раскрывается.</t>
+          <t>Группа проверяет учебный комплект документов допуска одного работника подрядчика: протоколы проверки знания, записи журнала инструктажей и стажировочный лист. По комплекту нужно решить, можно ли допустить работника к самостоятельной работе. Вывод записывают в бланк аудита и подтверждают пунктами стандарта. Если документов или записей не хватает для допуска, группа прямо указывает это в бланке.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>М-16.01.10-14, таблица 1, пункт 6.7.3, раздел 6.8, разделы 7.1–7.5. Шаблоны Ш-16.01.10-33–36 и Ш-16.01.10-03, Ш-16.01.10-04, Ш-16.01.10-37–40. Памятка участника.</t>
+          <t>М-16.01.10-14, таблица 1. Шаблоны протоколов Ш-16.01.10-33–36. Журналы Ш-16.01.10-03 и Ш-16.01.10-04. Стажировка Ш-16.01.10-37–40.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>uchastniku/05-audit-dopuska.md: протоколы, выписки журналов, лист стажировки и бланк аудита. Печатать как комплект личного дела, каждый документ с новой страницы.</t>
+          <t>Комплект «личного дела»: протоколы, скрин журнала, стажировочный лист. Бланк аудита.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>М-16.01.10-14, раздел 5.8, раздел 6.2, пункт 6.7.3, раздел 6.8, разделы 7.1–7.5. Сверка с Правилами № 2464, пункты 86–93.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="96" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+          <t>Раздел 5.8. Раздел 6.2. П. 6.7.3. Раздел 6.8. Разделы 7.1–7.5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="126" customHeight="1">
+      <c r="A7" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -678,32 +675,32 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>По ситуации на захвате группа готовит документы и проводит внеплановый инструктаж в ролях из задания 3. Нужны распоряжение, перечень работников, тезисы, устная проверка знания и запись в журнале. Эталон документов на этой вкладке не раскрывается.</t>
+          <t>Группа по вводной ситуации готовит документы и проводит внеплановый инструктаж в ролях из задания 3. Нужны локальный акт, перечень работников, тезисы инструктажа, проверка знания и запись в журнале. Каждая роль делает свою часть по матрице ответственности. Итог — проведенный инструктаж и заполненный комплект бланков.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>М-16.01.10-14, пункт 5.5.1, разделы 5.5, 5.7 и 5.8. Матрица ответственности, операции 15–18. Роли из задания 3. Журнал Ш-16.01.10-04.</t>
+          <t>М-16.01.10-14, п. 5.5.1 и разделы 5.5, 5.7, 5.8. Матрица ответственности, операции 15–18. Журнал Ш-16.01.10-04.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>uchastniku/06-vneplanovyj-instruktazh.md: ситуация и пустые бланки по числу ролевых троек. Карточки ролей из задания 3.</t>
+          <t>Вводная ситуация. Пустые бланки: распоряжение, перечень работников, тезисы инструктажа, лист регистрации, вопросы проверки знания. Карточки ролей из задания 3.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>М-16.01.10-14, пункт 5.5.1, разделы 5.5, 5.7 и 5.8. Сверка с Правилами № 2464, пункты 16–18, 22–24 и 87.</t>
+          <t>П. 5.5.1. Разделы 5.5, 5.7, 5.8.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F7"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;LТренинг. Сводка заданий</oddHeader>
-    <oddFooter/>
+    <oddHeader>&amp;LМ-16.01.10-14. Задания тренинга</oddHeader>
+    <oddFooter>&amp;RСтр. &amp;P</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/trening/navigator-narusheniya.xlsx
+++ b/trening/navigator-narusheniya.xlsx
@@ -9,12 +9,15 @@
   <sheets>
     <sheet name="Задания" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Навигатор" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Задание 1 — карточка" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Задания'!$A$1:$F$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Задания'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Навигатор'!$A$1:$D$41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Навигатор'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Задание 1 — карточка'!$A$2:$F$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Задание 1 — карточка'!$2:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,25 @@
       <name val="Calibri"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001A1A1A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +79,23 @@
         <fgColor rgb="00F3F6F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7EEF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D0D0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -82,11 +117,69 @@
         <color rgb="00D0D7DE"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -106,6 +199,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -514,33 +639,33 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="142" customHeight="1">
-      <c r="A2" s="5" t="n">
+    <row r="2" ht="120" customHeight="1">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Найди нарушения в процессе по видео</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Группа смотрит раскадровку работы подрядчика на площадке дочернего общества и фиксирует нарушения процесса допуска и обучения. На кадрах только работники подрядной организации: сотрудников ПАО «Газпром нефть» не показываем. Каждое нарушение группа подтверждает пунктом стандарта и записывает в бланк. В бланке остаются формулировка нарушения и ссылка на пункт, которым группа его подтвердила.</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>М-16.01.10-14, разделы 4 и 5. Матрица ответственности, блок инструктажей.</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Раскадровка видеокейса подрядчика. Бланк фиксации нарушений.</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Раздел 4. Раздел 5 (п. 5.1–5.8), в том числе п. 5.3.2 и п. 5.5.1.</t>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Речь подрядчика: как я проходил обучение</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Группа слушает речь слесаря подрядной организации о том, как он проходил обучение по охране труда, и сама делит услышанное на основания для недопуска и некритичные несоответствия. В речи только работник подрядчика: сотрудников ПАО «Газпром нефть» нет. Каждую позицию группа подтверждает разделом стандарта. Готовых выводов в раздатке нет.</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, разделы 4–7. Постановление Правительства РФ от 24.12.2021 № 2464.</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Текст речи подрядчика.</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Раздел 4. Раздел 5 (вводный и первичный инструктаж, проверка знания, журнал). Раздел 6 (таблицы 1 и 2, программы «А», «Б», «В», «ОПП», реестр). Раздел 7 (допуск к стажировке).</t>
         </is>
       </c>
     </row>
@@ -1639,4 +1764,427 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="168" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Артём Сергеевич Кожевников, слесарь по ремонту технологического оборудования ООО «СеверМонтаж», принятый 16 марта 2026 года, к самостоятельной работе не допущен. Основания: первичный инструктаж не завершён проверкой знания; к стажировке его допустили до обучения по охране труда; программа «Б» пройдена за 8 часов и без практического блока, для рабочей профессии в таком виде она недействительна; обучение первой помощи длилось 2 часа вместо не менее 8 и не содержит требуемой практики; навык сердечно-лёгочной реанимации он не выполнил, а протокол подписан по тесту и поэтому недостоверен.
+Сами по себе допуск не снимают: повтор вводного инструктажа без смены подрядной организации, лишняя программа «А», лишняя тема радиационной безопасности внутри программы «Б», убеждение, что работы на высоте можно учить только во внешнем учебном центре, и группа из 30 человек на практике по первой помощи. Жёсткого предела численности группы ни стандарт, ни постановление № 2464 не задают. Неподтверждённый навык реанимации при этом допуск всё равно блокирует, это отдельная строка, а не строка про число людей.</t>
+        </is>
+      </c>
+      <c r="B1" s="17" t="n"/>
+      <c r="C1" s="17" t="n"/>
+      <c r="D1" s="17" t="n"/>
+      <c r="E1" s="17" t="n"/>
+      <c r="F1" s="18" t="n"/>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Что прозвучало в речи</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>Несоответствие</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Влияние на допуск</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>Как должно быть</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>Куда смотреть</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="126" customHeight="1">
+      <c r="A3" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>«Вводный проходил дважды: вечером ещё раз видео, тест и подпись, хотя организацию не менял. По сути инструктаж один»</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Повтор вводного инструктажа работнику подрядчика в течение года без смены подрядной организации. Один инструктаж фактически проведён, вторая запись — дубль без основания</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Некритичное, на допуск не влияет</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Работникам подрядных организаций, которые периодически работают на территории ДО, вводный инструктаж проводят не чаще одного раза в год. Повторно в течение года — только если работник прекратил трудовые отношения с одной подрядной организацией и принят в другую. Видео, тест и подпись по фактически проведённому инструктажу норме соответствуют: видеофильм допустим, проверка знания обязательна, результат фиксируют в журнале</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, раздел 5.2 (повтор не чаще раза в год; видеофильм допускается), раздел 5.7, раздел 5.8. ПП РФ № 2464, пункт 10 (вводный до начала трудовых функций). Отдельного пункта Правил про запрет второго вводного подрядчику в течение года нет: это норма стандарта</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="156" customHeight="1">
+      <c r="A4" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>«Инструкции почитал, вопросов не было. 19 марта расписался в журнале, мастер тоже»</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Первичный инструктаж не завершён проверкой знания: не было ни устного опроса, ни письменной проверки, ни теста. Без проверки знания инструктаж не считается проведённым, а он обязателен до допуска к самостоятельной работе. То, что его проводил мастер, нарушением не является</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Основание для недопуска</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Первичный инструктаж проводят до начала самостоятельной работы, очно, по программе профессии. Проводит непосредственный руководитель: здесь это выполнено, Громов Илья Петрович — мастер. Проверка знания — неотъемлемая часть любого инструктажа. Форму задаёт распорядительный документ. Подпись в журнале без проверки знание не заменяет. Работника без инструктажа и проверки знания к работе не допускают. Несколько дней между приёмом и подписью сами по себе не брак: до подписи его к оборудованию не ставили</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, раздел 5.3, раздел 5.7, раздел 4. ПП РФ № 2464, пункт 13, пункт 22, пункт 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="111" customHeight="1">
+      <c r="A5" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>«На стажировке со старшим мастером две смены: обход, разборка фланца, замена прокладки, работа его инструментом. Курсов по охране труда к тем сменам ещё не было»</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>К стажировке допустили до обучения по охране труда. Стажировка шла раньше программ «Б», работ на высоте и первой помощи. Наставник, распоряжение и план ошибкой не являются</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Основание для недопуска</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>К стажировке допускают работников, которые уже прошли инструктаж, обучение и проверку знания. Слесарю, который выполняет работы повышенной опасности, до стажировки нужны программа «Б» и программы «В» по тем работам, которые он выполняет, а также первая помощь. Стажировка идёт после этого, очно, по программе, не менее двух смен</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, раздел 7.1, раздел 6.1, раздел 4, раздел 7.4. ПП РФ № 2464, пункт 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="111" customHeight="1">
+      <c r="A6" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>«Программу 46 „А“, общие вопросы охраны труда, прошёл. Сказали, что рабочим тоже положено»</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Программа «А» назначена работнику рабочей профессии. Она для руководителей, не для рабочих. Лишнее обучение само по себе допуск не отменяет, если обязательные программы пройдены верно. Здесь они не пройдены, но эта строка остаётся некритичной</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Некритичное, на допуск не влияет</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>По таблице 2 программу «А» проходят руководитель ДО и заместители с обязанностями по охране труда, руководители филиалов и их заместители, руководители структурных подразделений и иные руководители с работниками в подчинении. Строка «работники рабочих профессий» программу «А» не содержит: им внутреннее обучение по программе «Б», в том числе «ОПП»</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, раздел 6.5, таблица 2. ПП РФ № 2464, пункт 53 «а» и «б» (программа «а» — руководителям), пункт 53 «д» (рабочие профессии — программа «б»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="186" customHeight="1">
+      <c r="A7" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>«Программу 46 „Б“ прошёл дистанционно за восемь часов. Тест сложный, сдал. Практики не было: только экран и вопросы»</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Восемь часов вместо 16 и нет практического блока. Для слесаря программа «Б» обязательна, в таком объёме она недействительна. Дистанционная форма отдельной программы «Б» сама по себе нарушением не является</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Основание для недопуска</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Таблица 1: программа «Б» — 16 часов, из них 12 часов теории и 4 часа практики на Портале знаний. Четыре часа — это 25 процентов. Раздел 6.2 запрещает дистанционные технологии для практики программ «В», «ОПП» и «СИЗ», но не для практики отдельной программы «Б». Восьмичасовой курс без практического блока этим требованиям не отвечает. Пункт 66 Правил в редакции от 30.06.2026 № 805 запрещает дистанционно практику первой помощи, практику по СИЗ и занятия на полигонах и тренажёрах. Портальную практику отдельной программы «Б» этот запрет не закрывает, и стандарт её прямо задаёт. Бракуют часы и отсутствие практики, а не слово «дистанционно»</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, таблица 1 раздела 6.2, раздел 6.2, раздел 6.5, таблица 2, раздел 6.1, раздел 4. ПП РФ № 2464, пункт 46 «б», пункт 49, пункт 53 «д», пункт 66</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="126" customHeight="1">
+      <c r="A8" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>«В курсе „Б“ был блок про радиационную безопасность: источники излучения, дозиметры, как не зайти в зону. На ремонте оборудования такого нет»</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>В программу «Б» включена тема, которая не относится к трудовой функции слесаря по ремонту технологического оборудования. Это несоответствие содержания. Само по себе допуск не снимает</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Некритичное, на допуск не влияет</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Программа «Б» строится по опасностям, выявленным СОУТ и оценкой профессиональных рисков на работах этого работника, и по шаблону Ш-16.01.10-06. Работы с радиоактивными веществами и источниками ионизирующих излучений — отдельная программа «В» (приложение 1, шаблон Ш-16.01.10-22). Слесарю её не назначают, если он такие работы не выполняет. Лишняя тема не заменяет недостающий объём программы «Б»</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, раздел 6.1, раздел 6.2, приложение 1. ПП РФ № 2464, пункт 46 «б», пункт 49 (программа учитывает трудовые функции)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="111" customHeight="1">
+      <c r="A9" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>«Раз высота — значит только учебный центр, внутри компании учить нельзя, иначе допуск не признают»</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Работник подаёт обучение работам на высоте так, будто оно допустимо только во внешнем учебном центре. По стандарту его можно провести внутри организации. Учебный центр, полигон, СИЗ, два дня и экзамен нарушением не являются</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Некритичное, на допуск не влияет</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Исполнителю работ на высоте нужна программа «В». По таблице 2 работникам рабочих профессий, которые выполняют работы повышенной опасности, её проводят внутренне. Внешнее обучение тоже допускается, в том числе тем, кому можно учиться внутри. Два дня на полигоне с СИЗ и экзаменом короче нормы не делают: по таблице 1 программа «В» по высоте — 8 часов, из них 4 часа практики очно</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, раздел 6.1, раздел 6.5, таблица 2, таблица 1 раздела 6.2. ПП РФ № 2464, пункт 44 (обязательное внешнее обучение рабочих не включает), пункт 55, пункт 99</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="96" customHeight="1">
+      <c r="A10" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>«Первая помощь — два часа у тренажёра, сердечно-лёгочная реанимация»</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Два часа вместо не менее 8. Практический блок не выдержан: отдельная программа «ОПП» — 8 часов, из них 4 часа практики очно, то есть не менее 50 процентов. Двухчасовое занятие этот объём не закрывает. Обучение первой помощи в таком виде недействительно</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Основание для недопуска</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Таблица 1: программа «ОПП» отдельно от «Б» — 8 часов, теория 4 часа дистанционно, практика 4 часа очно. Практику по первой помощи дистанционно не проводят. Слесарю первая помощь обязательна и как работнику рабочей профессии, и как работнику на высоте. Без действительного обучения к самостоятельной работе не допускают</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, таблица 1 раздела 6.2, раздел 6.2, раздел 6.5, таблица 2, раздел 4. ПП РФ № 2464, пункт 33 «б», пункт 36, пункт 66</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="111" customHeight="1">
+      <c r="A11" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>«На практике по первой помощи в группе было 30 человек, все у одного манекена»</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Организация практики: при 30 человеках и двух часах у одного тренажёра каждый не отрабатывает навык. С этим совпадает то, что сам Кожевников тренажёр не реанимировал. Числового предела группы стандарт и постановление № 2464 не устанавливают, поэтому цифру 30 как нарушение лимита не квалифицируют</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Некритичное, на допуск не влияет</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Жёсткого лимита «не более N человек» в тексте нет, выдуманную цифру не применяем. Практика первой помощи должна дать каждому навык на тренажёре: 4 часа очно внутри программы не короче 8 часов. Неподтверждённый навык реанимации допуск блокирует строкой 10, а не численность сама по себе</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, раздел 6.2, таблица 1. ПП РФ № 2464, пункт 36. Пункта о предельной численности группы нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="81" customHeight="1">
+      <c r="A12" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>«Тренажёр не ожил. Тест сдал, протокол подписал, оценка положительная»</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Практический навык сердечно-лёгочной реанимации не выполнен, а протокол проверки знания подписан по результатам теста. Проверка по первой помощи включает умения и навыки. Протокол недостоверен</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Основание для недопуска</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>Проверка по программе «ОПП» — это проверка знаний, умений и навыков, а не только письменный тест. Невыполненный навык нельзя закрыть оценкой за тест. Без достоверной проверки знания работника к работе не допускают</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, раздел 6.6, раздел 4. ПП РФ № 2464, пункт 37</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="126" customHeight="1">
+      <c r="A13" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>«На Госуслуги пришло уведомление, что проверку знаний прошёл. Значит, я допущен и все работы выполняю»</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Итог. Ложный вывод: уведомление на Госуслугах принято за допуск к самостоятельной работе. Регистрация протокола в реестре обученных лиц и само уведомление нарушением не являются</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Основание для недопуска</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>Допуск к самостоятельной работе — после инструктажей с проверкой знания, обучения по всем программам своей категории в нужном объёме и стажировки, которая начинается уже после этого обучения. Запись в реестре подтверждает переданные сведения о проверке знания, а не закрывает пробелы. Отдельного пункта Правил про уведомление на Госуслугах нет: уведомление не бракуем и номер ему не придумываем</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, раздел 4, раздел 6.1, раздел 6.8. ПП РФ № 2464, пункт 118. Пункта про уведомление на Госуслугах в Правилах нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Подсказка тренеру. Сначала слушаем речь. Группа сама делит услышанное на «недопуск» и «некритичное». Карточку открывают после попытки и сверяют список. Красная заливка — основание для недопуска. Жёлтая — некритичное, на допуск не влияет.</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="18" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:F13"/>
+  <mergeCells count="2">
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;LЗадание 1. Карточка несоответствий. Только для тренера</oddHeader>
+    <oddFooter>&amp;RСтр. &amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/trening/navigator-narusheniya.xlsx
+++ b/trening/navigator-narusheniya.xlsx
@@ -2158,10 +2158,10 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1">
+    <row r="14" ht="52" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Подсказка тренеру. Сначала слушаем речь. Группа сама делит услышанное на «недопуск» и «некритичное». Карточку открывают после попытки и сверяют список. Красная заливка — основание для недопуска. Жёлтая — некритичное, на допуск не влияет.</t>
+          <t>Подсказка тренеру. Сначала слушаем речь. Группа сама делит услышанное на «недопуск» и «некритичное». Карточку открывают после попытки и сверяют список. Красная заливка — основание для недопуска. Жёлтая — некритичное, на допуск не влияет. Бытовой шум в таблицу не входит: характер тренера, скука, засыпал над курсом, погода, кофе, каска, журнал искали. На разборе спросите, почему это отбросили.</t>
         </is>
       </c>
       <c r="B14" s="17" t="n"/>

--- a/trening/navigator-narusheniya.xlsx
+++ b/trening/navigator-narusheniya.xlsx
@@ -95,7 +95,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -175,11 +175,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -231,6 +232,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1783,11 +1788,12 @@
     <col width="46" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="168" customHeight="1">
+    <row r="1" ht="132" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Артём Сергеевич Кожевников, слесарь по ремонту технологического оборудования ООО «СеверМонтаж», принятый 16 марта 2026 года, к самостоятельной работе не допущен. Основания: первичный инструктаж не завершён проверкой знания; к стажировке его допустили до обучения по охране труда; программа «Б» пройдена за 8 часов и без практического блока, для рабочей профессии в таком виде она недействительна; обучение первой помощи длилось 2 часа вместо не менее 8 и не содержит требуемой практики; навык сердечно-лёгочной реанимации он не выполнил, а протокол подписан по тесту и поэтому недостоверен.
-Сами по себе допуск не снимают: повтор вводного инструктажа без смены подрядной организации, лишняя программа «А», лишняя тема радиационной безопасности внутри программы «Б», убеждение, что работы на высоте можно учить только во внешнем учебном центре, и группа из 30 человек на практике по первой помощи. Жёсткого предела численности группы ни стандарт, ни постановление № 2464 не задают. Неподтверждённый навык реанимации при этом допуск всё равно блокирует, это отдельная строка, а не строка про число людей.</t>
+          <t>Артём Сергеевич Кожевников, слесарь по ремонту технологического оборудования ООО «СеверМонтаж», принятый 16 августа 2026 года, к самостоятельной работе не допущен. Основания: первичный инструктаж не завершён проверкой знания; к стажировке его допустили до обучения по охране труда; программа безопасных методов (программа «Б») пройдена за 3 часа и без практического блока, для рабочей профессии в таком виде она недействительна; обучение первой помощи длилось 2 часа вместо не менее 8 и не содержит требуемой практики; навык сердечно-лёгочной реанимации он не выполнил, а протокол подписан по тесту и поэтому недостоверен. Уведомление на Госуслугах он принял за допуск. В речи одно такое уведомление, про уведомления по другим обучениям ничего не сказано.
+Сами по себе допуск не снимают: программа общих вопросов охраны труда и системы управления (программа «А») у рабочей профессии, лишние темы радиационной безопасности и биологического фактора внутри программы «Б», группа из 30 человек на практике по первой помощи. Жёсткого предела численности группы ни стандарт, ни постановление № 2464 не задают. Неподтверждённый навык реанимации при этом допуск всё равно блокирует, это отдельная строка, а не строка про число людей.
+Повтор вводного инструктажа через три месяца несоответствием не является: он уже проходил его, работая в ООО «Спецремонт», а теперь принят в другую подрядную организацию. Учебный центр по высоте, полигон, страховочные системы, два дня и экзамен нарушением не являются.</t>
         </is>
       </c>
       <c r="B1" s="17" t="n"/>
@@ -1828,48 +1834,48 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="126" customHeight="1">
-      <c r="A3" s="12" t="n">
+    <row r="3" ht="130" customHeight="1">
+      <c r="A3" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>«Вводный проходил дважды: вечером ещё раз видео, тест и подпись, хотя организацию не менял. По сути инструктаж один»</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>Повтор вводного инструктажа работнику подрядчика в течение года без смены подрядной организации. Один инструктаж фактически проведён, вторая запись — дубль без основания</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>Некритичное, на допуск не влияет</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr">
-        <is>
-          <t>Работникам подрядных организаций, которые периодически работают на территории ДО, вводный инструктаж проводят не чаще одного раза в год. Повторно в течение года — только если работник прекратил трудовые отношения с одной подрядной организацией и принят в другую. Видео, тест и подпись по фактически проведённому инструктажу норме соответствуют: видеофильм допустим, проверка знания обязательна, результат фиксируют в журнале</t>
-        </is>
-      </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>М-16.01.10-14, раздел 5.2 (повтор не чаще раза в год; видеофильм допускается), раздел 5.7, раздел 5.8. ПП РФ № 2464, пункт 10 (вводный до начала трудовых функций). Отдельного пункта Правил про запрет второго вводного подрядчику в течение года нет: это норма стандарта</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="156" customHeight="1">
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>«Инструкции до конца не дочитал: слишком текста много. Вопросов не было. 19 августа расписался в журнале, мастер тоже»</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Первичный инструктаж без проверки знания. Подпись её не заменяет. То, что он не дочитал инструкции, отдельной строкой не бракуется: в проверенной карточке нет нормы, по которой непрочитанный до конца текст сам по себе отменяет инструктаж. То, что проводил мастер, нарушением не является</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Основание для недопуска</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>Проверка знания — часть инструктажа. Проводит непосредственный руководитель, здесь это выполнено, Громов Илья Петрович — мастер. Первичный инструктаж проводят до начала самостоятельной работы, очно, по программе профессии. Форму проверки задаёт распорядительный документ. Подпись в журнале без проверки знание не заменяет. Работника без инструктажа и проверки знания к работе не допускают. Несколько дней между приёмом 16 августа и подписью 19 августа сами по себе не брак: до подписи его к оборудованию не ставили</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, раздел 5.3, раздел 5.7, раздел 4. ПП РФ № 2464, пункт 13, пункт 22, пункт 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="120" customHeight="1">
       <c r="A4" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>«Инструкции почитал, вопросов не было. 19 марта расписался в журнале, мастер тоже»</t>
+          <t>«Стажировка две смены со старшим мастером: обход, разборка фланца, замена прокладки, работа его инструментом. Уже после этих смен посадили учиться»</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>Первичный инструктаж не завершён проверкой знания: не было ни устного опроса, ни письменной проверки, ни теста. Без проверки знания инструктаж не считается проведённым, а он обязателен до допуска к самостоятельной работе. То, что его проводил мастер, нарушением не является</t>
+          <t>Допуск к стажировке до обучения по охране труда. Стажировка шла раньше программ безопасных методов, высоты и первой помощи. Наставник, распоряжение и план ошибкой не являются</t>
         </is>
       </c>
       <c r="D4" s="14" t="inlineStr">
@@ -1879,147 +1885,147 @@
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>Первичный инструктаж проводят до начала самостоятельной работы, очно, по программе профессии. Проводит непосредственный руководитель: здесь это выполнено, Громов Илья Петрович — мастер. Проверка знания — неотъемлемая часть любого инструктажа. Форму задаёт распорядительный документ. Подпись в журнале без проверки знание не заменяет. Работника без инструктажа и проверки знания к работе не допускают. Несколько дней между приёмом и подписью сами по себе не брак: до подписи его к оборудованию не ставили</t>
+          <t>Сначала инструктаж, обучение и проверка знания, потом стажировка, не менее двух смен. Слесарю, который выполняет работы повышенной опасности, до стажировки нужны программа «Б» и программы «В» по тем работам, которые он выполняет, а также первая помощь. Стажировка идёт после этого, очно, по программе</t>
         </is>
       </c>
       <c r="F4" s="15" t="inlineStr">
         <is>
-          <t>М-16.01.10-14, раздел 5.3, раздел 5.7, раздел 4. ПП РФ № 2464, пункт 13, пункт 22, пункт 23</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="111" customHeight="1">
-      <c r="A5" s="14" t="n">
+          <t>М-16.01.10-14, раздел 7.1, раздел 6.1, раздел 4, раздел 7.4. ПП РФ № 2464, пункт 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="130" customHeight="1">
+      <c r="A5" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>«На стажировке со старшим мастером две смены: обход, разборка фланца, замена прокладки, работа его инструментом. Курсов по охране труда к тем сменам ещё не было»</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>К стажировке допустили до обучения по охране труда. Стажировка шла раньше программ «Б», работ на высоте и первой помощи. Наставник, распоряжение и план ошибкой не являются</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>«Сначала первая программа, общие вопросы охраны труда и как устроена система управления. Курс короткий, про политику и про обязанности»</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Программа «А» назначена работнику рабочей профессии. В речи нет слов «46 „А“» и нет фразы, что рабочим она тоже положена: программу узнают по темам, это общие вопросы и система управления, она для руководителей. Лишнее обучение само по себе допуск не отменяет, если обязательные программы пройдены верно. Здесь они не пройдены, но эта строка остаётся некритичной. Часы этой программы в речи не названы, отдельный брак по продолжительности не ставлю</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Некритичное, на допуск не влияет</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Рабочим — программа «Б», в том числе «ОПП». Лишняя «А» допуск сама не снимает. По таблице 2 программу «А» проходят руководитель ДО и заместители с обязанностями по охране труда, руководители филиалов и их заместители, руководители структурных подразделений и иные руководители с работниками в подчинении. Строка «работники рабочих профессий» программу «А» не содержит</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, раздел 6.5, таблица 2. ПП РФ № 2464, пункт 53 «а» и «б» (программа «а» — руководителям), пункт 53 «д» (рабочие профессии — программа «б»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>«Программа про безопасные методы и приемы, дистанционный курс. Сидел вечерами по часу в день, уложился за три дня. Тест сдал. Практики не было: только экран и вопросы»</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>3 часа вместо 16 и нет практического блока. Для слесаря программа «Б» обязательна, в таком объёме она недействительна. Дистанционная форма отдельной программы «Б» сама по себе не брак. «По часу в день, три дня» — это три часа, не восемь</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Основание для недопуска</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>К стажировке допускают работников, которые уже прошли инструктаж, обучение и проверку знания. Слесарю, который выполняет работы повышенной опасности, до стажировки нужны программа «Б» и программы «В» по тем работам, которые он выполняет, а также первая помощь. Стажировка идёт после этого, очно, по программе, не менее двух смен</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="inlineStr">
-        <is>
-          <t>М-16.01.10-14, раздел 7.1, раздел 6.1, раздел 4, раздел 7.4. ПП РФ № 2464, пункт 25</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="111" customHeight="1">
-      <c r="A6" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>«Программу 46 „А“, общие вопросы охраны труда, прошёл. Сказали, что рабочим тоже положено»</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Программа «А» назначена работнику рабочей профессии. Она для руководителей, не для рабочих. Лишнее обучение само по себе допуск не отменяет, если обязательные программы пройдены верно. Здесь они не пройдены, но эта строка остаётся некритичной</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>16 часов: 12 теории и 4 практики на Портале знаний. Четыре часа — это 25 процентов. Раздел 6.2 запрещает дистанционные технологии для практики программ «В», «ОПП» и «СИЗ», но не для практики отдельной программы «Б». Трёхчасовой курс без практического блока этим требованиям не отвечает. Пункт 66 Правил в редакции от 30.06.2026 № 805 запрещает дистанционно практику первой помощи, практику по СИЗ и занятия на полигонах и тренажёрах. Портальную практику отдельной программы «Б» этот запрет не закрывает, и стандарт её прямо задаёт. Бракуют часы и отсутствие практики, а не слово «дистанционно» и не то, что сидел вечерами</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, таблица 1 раздела 6.2, раздел 6.2, раздел 6.5, таблица 2, раздел 6.1, раздел 4. ПП РФ № 2464, пункт 46 «б», пункт 49, пункт 53 «д», пункт 66</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="130" customHeight="1">
+      <c r="A7" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>«В курсе был блок про радиационную безопасность и биологический фактор. На ремонте оборудования такого нет»</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>В программу «Б» включены темы, которые не относятся к трудовой функции слесаря по ремонту технологического оборудования. Это несоответствие содержания. Само по себе допуск не снимает</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Некритичное, на допуск не влияет</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>По таблице 2 программу «А» проходят руководитель ДО и заместители с обязанностями по охране труда, руководители филиалов и их заместители, руководители структурных подразделений и иные руководители с работниками в подчинении. Строка «работники рабочих профессий» программу «А» не содержит: им внутреннее обучение по программе «Б», в том числе «ОПП»</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>М-16.01.10-14, раздел 6.5, таблица 2. ПП РФ № 2464, пункт 53 «а» и «б» (программа «а» — руководителям), пункт 53 «д» (рабочие профессии — программа «б»)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="186" customHeight="1">
-      <c r="A7" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>«Программу 46 „Б“ прошёл дистанционно за восемь часов. Тест сложный, сдал. Практики не было: только экран и вопросы»</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Восемь часов вместо 16 и нет практического блока. Для слесаря программа «Б» обязательна, в таком объёме она недействительна. Дистанционная форма отдельной программы «Б» сама по себе нарушением не является</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Программу «Б» собирают по опасностям его работ, по СОУТ и оценке профессиональных рисков, и по шаблону Ш-16.01.10-06. Работы с радиоактивными веществами и источниками ионизирующих излучений — отдельная программа «В» (приложение 1, шаблон Ш-16.01.10-22). Слесарю её не назначают, если он такие работы не выполняет. Отдельный шаблон по биологическому фактору в проверенной карточке не найден, номер не придумываю: тема лишняя по тому же основанию, программа учитывает трудовые функции. Лишние темы не заменяют недостающий объём программы «Б»</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, раздел 6.1, раздел 6.2, приложение 1. ПП РФ № 2464, пункт 46 «б», пункт 49 (программа учитывает трудовые функции)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="110" customHeight="1">
+      <c r="A8" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>«Первая помощь — два часа у тренажёра, сердечно-лёгочная реанимация»</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>2 часа вместо 8, практика не выдержана. Отдельная программа «ОПП» — 8 часов, из них 4 часа практики очно, то есть не менее 50 процентов. Двухчасовое занятие этот объём не закрывает. Обучение первой помощи в таком виде недействительно</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Основание для недопуска</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>Таблица 1: программа «Б» — 16 часов, из них 12 часов теории и 4 часа практики на Портале знаний. Четыре часа — это 25 процентов. Раздел 6.2 запрещает дистанционные технологии для практики программ «В», «ОПП» и «СИЗ», но не для практики отдельной программы «Б». Восьмичасовой курс без практического блока этим требованиям не отвечает. Пункт 66 Правил в редакции от 30.06.2026 № 805 запрещает дистанционно практику первой помощи, практику по СИЗ и занятия на полигонах и тренажёрах. Портальную практику отдельной программы «Б» этот запрет не закрывает, и стандарт её прямо задаёт. Бракуют часы и отсутствие практики, а не слово «дистанционно»</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>М-16.01.10-14, таблица 1 раздела 6.2, раздел 6.2, раздел 6.5, таблица 2, раздел 6.1, раздел 4. ПП РФ № 2464, пункт 46 «б», пункт 49, пункт 53 «д», пункт 66</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="126" customHeight="1">
-      <c r="A8" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>«В курсе „Б“ был блок про радиационную безопасность: источники излучения, дозиметры, как не зайти в зону. На ремонте оборудования такого нет»</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>В программу «Б» включена тема, которая не относится к трудовой функции слесаря по ремонту технологического оборудования. Это несоответствие содержания. Само по себе допуск не снимает</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Некритичное, на допуск не влияет</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>Программа «Б» строится по опасностям, выявленным СОУТ и оценкой профессиональных рисков на работах этого работника, и по шаблону Ш-16.01.10-06. Работы с радиоактивными веществами и источниками ионизирующих излучений — отдельная программа «В» (приложение 1, шаблон Ш-16.01.10-22). Слесарю её не назначают, если он такие работы не выполняет. Лишняя тема не заменяет недостающий объём программы «Б»</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>М-16.01.10-14, раздел 6.1, раздел 6.2, приложение 1. ПП РФ № 2464, пункт 46 «б», пункт 49 (программа учитывает трудовые функции)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="111" customHeight="1">
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Программа «ОПП»: 8 часов, из них 4 часа практики очно. По таблице 1 теория 4 часа дистанционно, практика 4 часа очно. Практику по первой помощи дистанционно не проводят. Слесарю первая помощь обязательна и как работнику рабочей профессии, и как работнику на высоте. Без действительного обучения к самостоятельной работе не допускают</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, таблица 1 раздела 6.2, раздел 6.2, раздел 6.5, таблица 2, раздел 4. ПП РФ № 2464, пункт 33 «б», пункт 36, пункт 66</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="110" customHeight="1">
       <c r="A9" s="12" t="n">
         <v>7</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>«Раз высота — значит только учебный центр, внутри компании учить нельзя, иначе допуск не признают»</t>
+          <t>«В группе 30 человек у одного манекена»</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Работник подаёт обучение работам на высоте так, будто оно допустимо только во внешнем учебном центре. По стандарту его можно провести внутри организации. Учебный центр, полигон, СИЗ, два дня и экзамен нарушением не являются</t>
+          <t>При такой организации каждый не отрабатывает навык. С этим совпадает то, что сам Кожевников тренажёр не реанимировал. Числового лимита группы стандарт и № 2464 не задают</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -2029,27 +2035,27 @@
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>Исполнителю работ на высоте нужна программа «В». По таблице 2 работникам рабочих профессий, которые выполняют работы повышенной опасности, её проводят внутренне. Внешнее обучение тоже допускается, в том числе тем, кому можно учиться внутри. Два дня на полигоне с СИЗ и экзаменом короче нормы не делают: по таблице 1 программа «В» по высоте — 8 часов, из них 4 часа практики очно</t>
+          <t>Навык должен получить каждый. Жёсткого лимита «не более N человек» в тексте нет, выдуманную цифру не применяем. Практика первой помощи должна дать каждому навык на тренажёре: 4 часа очно внутри программы не короче 8 часов. Неподтверждённая реанимация блокирует допуск строкой 8, а не численность сама по себе</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>М-16.01.10-14, раздел 6.1, раздел 6.5, таблица 2, таблица 1 раздела 6.2. ПП РФ № 2464, пункт 44 (обязательное внешнее обучение рабочих не включает), пункт 55, пункт 99</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="96" customHeight="1">
+          <t>М-16.01.10-14, раздел 6.2, таблица 1. ПП РФ № 2464, пункт 36. Пункта о предельной численности группы нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="100" customHeight="1">
       <c r="A10" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>«Первая помощь — два часа у тренажёра, сердечно-лёгочная реанимация»</t>
+          <t>«Тренажёр не ожил, тест сдал, протокол подписал, оценка положительная»</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Два часа вместо не менее 8. Практический блок не выдержан: отдельная программа «ОПП» — 8 часов, из них 4 часа практики очно, то есть не менее 50 процентов. Двухчасовое занятие этот объём не закрывает. Обучение первой помощи в таком виде недействительно</t>
+          <t>Навык сердечно-лёгочной реанимации не выполнен, протокол подписан по тесту. Проверка по первой помощи включает умения и навыки. Протокол недостоверен</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
@@ -2059,122 +2065,73 @@
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>Таблица 1: программа «ОПП» отдельно от «Б» — 8 часов, теория 4 часа дистанционно, практика 4 часа очно. Практику по первой помощи дистанционно не проводят. Слесарю первая помощь обязательна и как работнику рабочей профессии, и как работнику на высоте. Без действительного обучения к самостоятельной работе не допускают</t>
+          <t>Проверка по первой помощи включает умения и навыки, не только тест. Проверка по программе «ОПП» — это проверка знаний, умений и навыков. Невыполненный навык нельзя закрыть оценкой за тест. Без достоверной проверки знания работника к работе не допускают</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>М-16.01.10-14, таблица 1 раздела 6.2, раздел 6.2, раздел 6.5, таблица 2, раздел 4. ПП РФ № 2464, пункт 33 «б», пункт 36, пункт 66</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="111" customHeight="1">
-      <c r="A11" s="12" t="n">
+          <t>М-16.01.10-14, раздел 6.6, раздел 4. ПП РФ № 2464, пункт 37</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="130" customHeight="1">
+      <c r="A11" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>«На практике по первой помощи в группе было 30 человек, все у одного манекена»</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Организация практики: при 30 человеках и двух часах у одного тренажёра каждый не отрабатывает навык. С этим совпадает то, что сам Кожевников тренажёр не реанимировал. Числового предела группы стандарт и постановление № 2464 не устанавливают, поэтому цифру 30 как нарушение лимита не квалифицируют</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Некритичное, на допуск не влияет</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>Жёсткого лимита «не более N человек» в тексте нет, выдуманную цифру не применяем. Практика первой помощи должна дать каждому навык на тренажёре: 4 часа очно внутри программы не короче 8 часов. Неподтверждённый навык реанимации допуск блокирует строкой 10, а не численность сама по себе</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>М-16.01.10-14, раздел 6.2, таблица 1. ПП РФ № 2464, пункт 36. Пункта о предельной численности группы нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="81" customHeight="1">
-      <c r="A12" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>«Тренажёр не ожил. Тест сдал, протокол подписал, оценка положительная»</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Практический навык сердечно-лёгочной реанимации не выполнен, а протокол проверки знания подписан по результатам теста. Проверка по первой помощи включает умения и навыки. Протокол недостоверен</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>«На Госуслуги пришло уведомление, значит, допущен и все свои работы выполняю»</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Уведомление принято за допуск. Сама регистрация в реестре нарушением не является. В речи одно уведомление: «проверку знаний прошёл». Про уведомление о других обучениях ничего не сказано</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>Основание для недопуска</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>Проверка по программе «ОПП» — это проверка знаний, умений и навыков, а не только письменный тест. Невыполненный навык нельзя закрыть оценкой за тест. Без достоверной проверки знания работника к работе не допускают</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="inlineStr">
-        <is>
-          <t>М-16.01.10-14, раздел 6.6, раздел 4. ПП РФ № 2464, пункт 37</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="126" customHeight="1">
-      <c r="A13" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>«На Госуслуги пришло уведомление, что проверку знаний прошёл. Значит, я допущен и все работы выполняю»</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Итог. Ложный вывод: уведомление на Госуслугах принято за допуск к самостоятельной работе. Регистрация протокола в реестре обученных лиц и само уведомление нарушением не являются</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>Основание для недопуска</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>Допуск к самостоятельной работе — после инструктажей с проверкой знания, обучения по всем программам своей категории в нужном объёме и стажировки, которая начинается уже после этого обучения. Запись в реестре подтверждает переданные сведения о проверке знания, а не закрывает пробелы. Отдельного пункта Правил про уведомление на Госуслугах нет: уведомление не бракуем и номер ему не придумываем</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Допуск к самостоятельной работе — после инструктажей с проверкой знания, обучения по всем программам своей категории в нужном объёме и стажировки, которая начинается уже после этого обучения. Запись в реестре подтверждает переданные сведения о проверке знания, а не закрывает пробелы. Обратить внимание: про уведомление о других обучениях ничего не сказано. Отдельного пункта Правил про уведомление на Госуслугах нет: уведомление не бракуем и номер ему не придумываем</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>М-16.01.10-14, раздел 4, раздел 6.1, раздел 6.8. ПП РФ № 2464, пункт 118. Пункта про уведомление на Госуслугах в Правилах нет</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Подсказка тренеру. Сначала слушаем речь. Группа сама делит услышанное на «недопуск» и «некритичное». Карточку открывают после попытки и сверяют список. Красная заливка — основание для недопуска. Жёлтая — некритичное, на допуск не влияет. Бытовой шум в таблицу не входит: характер тренера, скука, засыпал над курсом, погода, кофе, каска, журнал искали. На разборе спросите, почему это отбросили.</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="17" t="n"/>
-      <c r="D14" s="17" t="n"/>
-      <c r="E14" s="17" t="n"/>
-      <c r="F14" s="18" t="n"/>
+    <row r="12" ht="78" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Подсказка тренеру. Сначала слушаем речь или смотрим видео. Группа сама делит услышанное на «недопуск» и «некритичное». Карточку открывают после попытки и сверяют список. Красная заливка — основание для недопуска. Жёлтая — некритичное, на допуск не влияет. В таблицу не входят: повтор вводного после ООО «Спецремонт» (раздел 5.2 разрешает повтор в течение года при смене подрядной организации); учебный центр, полигон, два дня и экзамен по высоте; «сидел вечерами» как «не в рабочее время» (в проверенной карточке пункта нет, номер не придумываем); быт — скука, характер преподавателя, шутки старшего мастера. На разборе спросите, почему это отбросили.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="n"/>
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="20" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="n"/>
+      <c r="B14" s="20" t="n"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="20" t="n"/>
+      <c r="F14" s="20" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:F13"/>
   <mergeCells count="2">
-    <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>

--- a/trening/navigator-narusheniya.xlsx
+++ b/trening/navigator-narusheniya.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Задания" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Навигатор" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Задание 1 — карточка" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Задания" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Навигатор" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Задание 1 — карточка" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Задания'!$A$1:$F$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Задания'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Навигатор'!$A$1:$D$41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Навигатор'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Задание 1 — карточка'!$A$2:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Задание 1 — карточка'!$A$2:$F$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Задание 1 — карточка'!$2:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -180,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -236,6 +236,11 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1777,7 +1782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1788,12 +1793,12 @@
     <col width="46" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="132" customHeight="1">
+    <row r="1" ht="150" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Артём Сергеевич Кожевников, слесарь по ремонту технологического оборудования ООО «СеверМонтаж», принятый 16 августа 2026 года, к самостоятельной работе не допущен. Основания: первичный инструктаж не завершён проверкой знания; к стажировке его допустили до обучения по охране труда; программа безопасных методов (программа «Б») пройдена за 3 часа и без практического блока, для рабочей профессии в таком виде она недействительна; обучение первой помощи длилось 2 часа вместо не менее 8 и не содержит требуемой практики; навык сердечно-лёгочной реанимации он не выполнил, а протокол подписан по тесту и поэтому недостоверен. Уведомление на Госуслугах он принял за допуск. В речи одно такое уведомление, про уведомления по другим обучениям ничего не сказано.
-Сами по себе допуск не снимают: программа общих вопросов охраны труда и системы управления (программа «А») у рабочей профессии, лишние темы радиационной безопасности и биологического фактора внутри программы «Б», группа из 30 человек на практике по первой помощи. Жёсткого предела численности группы ни стандарт, ни постановление № 2464 не задают. Неподтверждённый навык реанимации при этом допуск всё равно блокирует, это отдельная строка, а не строка про число людей.
-Повтор вводного инструктажа через три месяца несоответствием не является: он уже проходил его, работая в ООО «Спецремонт», а теперь принят в другую подрядную организацию. Учебный центр по высоте, полигон, страховочные системы, два дня и экзамен нарушением не являются.</t>
+          <t>Артём Сергеевич Кожевников, слесарь по ремонту технологического оборудования ООО «СеверМонтаж», принятый 16 августа 2026 года, к самостоятельной работе не допущен. Основания: первичный инструктаж не завершён проверкой знания; к стажировке его допустили до обучения по охране труда; программа безопасных методов (программа «Б») пройдена за 3 часа и без практического блока; обучение первой помощи длилось 2 часа вместо 8, практика не выдержана; навык сердечно-лёгочной реанимации не выполнен, протокол подписан по тесту. Уведомление на Госуслугах он принял за допуск. В речи одно такое уведомление, про уведомления по другим обучениям ничего не сказано.
+Сами по себе допуск не снимают: программа общих вопросов охраны труда и системы управления (программа «А») у рабочей профессии; лишние темы радиационной безопасности и биологического фактора внутри программы «Б»; группа из 30 человек на практике по первой помощи; два обучения на высоте. Два обучения — двойная трата бюджета, не основание для недопуска. Жёсткого предела численности группы ни стандарт, ни постановление № 2464 не задают. Неподтверждённый навык реанимации при этом допуск всё равно блокирует, это строка 10, а не строка про число людей.
+Повтор вводного инструктажа через три месяца несоответствием не является: он уже проходил его, работая в ООО «Спецремонт», а теперь принят в другую подрядную организацию. Учебный центр по высоте, полигон, страховочные системы, два дня и экзамен нарушением не являются. Фразы «только учебный центр, внутри учить нельзя» в речи нет.</t>
         </is>
       </c>
       <c r="B1" s="17" t="n"/>
@@ -1834,309 +1839,412 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="130" customHeight="1">
-      <c r="A3" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>«Инструкции до конца не дочитал: слишком текста много. Вопросов не было. 19 августа расписался в журнале, мастер тоже»</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>Первичный инструктаж без проверки знания. Подпись её не заменяет. То, что он не дочитал инструкции, отдельной строкой не бракуется: в проверенной карточке нет нормы, по которой непрочитанный до конца текст сам по себе отменяет инструктаж. То, что проводил мастер, нарушением не является</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
+    <row r="3" ht="84" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>«Вводный на КПП: видео минут двадцать, тест, подпись. Три месяца назад этот инструктаж уже проходил, когда работал в ООО «Спецремонт». Сейчас принят в ООО «СеверМонтаж»»</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Несоответствия нет. В таблице решения повтор назван дублем без смены организации. В речи организация сменилась. Такой повтор в течение года норма разрешает. Видео, тест и подпись норме соответствуют</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>На допуск не влияет</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Не чаще одного раза в год. Повтор в течение года — только при переходе в другую подрядную организацию. Видео, тест и подпись норме соответствуют</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, раздел 5.2. ПП РФ № 2464, пункт 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="102" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>«Инструкции до конца не дочитал: слишком много текста. Вопросов не было: ни устно, ни на бумаге, ни на компьютере. 19 августа расписался, мастер тоже»</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Первичный инструктаж без проверки знания. Подпись её не заменяет. То, что он не дочитал инструкции, отдельной строкой не бракуется. То, что проводил мастер, нарушением не является</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Основание для недопуска</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>Проверка знания — часть инструктажа. Проводит непосредственный руководитель, здесь это выполнено, Громов Илья Петрович — мастер. Первичный инструктаж проводят до начала самостоятельной работы, очно, по программе профессии. Форму проверки задаёт распорядительный документ. Подпись в журнале без проверки знание не заменяет. Работника без инструктажа и проверки знания к работе не допускают. Несколько дней между приёмом 16 августа и подписью 19 августа сами по себе не брак: до подписи его к оборудованию не ставили</t>
-        </is>
-      </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Проверка знания — часть инструктажа. Проводит непосредственный руководитель, здесь это выполнено, Громов Илья Петрович — мастер. Подпись в журнале без проверки знание не заменяет. До подписи 19 августа его к оборудованию не ставили</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>М-16.01.10-14, раздел 5.3, раздел 5.7, раздел 4. ПП РФ № 2464, пункт 13, пункт 22, пункт 23</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="120" customHeight="1">
-      <c r="A4" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>«Стажировка две смены со старшим мастером: обход, разборка фланца, замена прокладки, работа его инструментом. Уже после этих смен посадили учиться»</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>Допуск к стажировке до обучения по охране труда. Стажировка шла раньше программ безопасных методов, высоты и первой помощи. Наставник, распоряжение и план ошибкой не являются</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
+    <row r="5" ht="66" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>«Стажировка две смены до курсов по охране труда. Распоряжение и план были. Наставник — старший мастер Леонтьев. Уже после этих смен посадили учиться»</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Допуск к стажировке до обучения по охране труда. Наставник и план ошибкой не являются</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Основание для недопуска</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>Сначала инструктаж, обучение и проверка знания, потом стажировка, не менее двух смен. Слесарю, который выполняет работы повышенной опасности, до стажировки нужны программа «Б» и программы «В» по тем работам, которые он выполняет, а также первая помощь. Стажировка идёт после этого, очно, по программе</t>
-        </is>
-      </c>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>М-16.01.10-14, раздел 7.1, раздел 6.1, раздел 4, раздел 7.4. ПП РФ № 2464, пункт 25</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="130" customHeight="1">
-      <c r="A5" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>Сначала инструктаж, обучение и проверка знания, потом стажировка, не менее двух смен</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, раздел 7.1, раздел 6.1, раздел 4, раздел 7.4. ПП РФ № 2464, пункт 25, пункт 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="84" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>«Сначала первая программа, общие вопросы охраны труда и как устроена система управления. Курс короткий, про политику и про обязанности»</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Программа «А» назначена работнику рабочей профессии. В речи нет слов «46 „А“» и нет фразы, что рабочим она тоже положена: программу узнают по темам, это общие вопросы и система управления, она для руководителей. Лишнее обучение само по себе допуск не отменяет, если обязательные программы пройдены верно. Здесь они не пройдены, но эта строка остаётся некритичной. Часы этой программы в речи не названы, отдельный брак по продолжительности не ставлю</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Программа «А» назначена рабочей профессии. Она для руководителей. В речи нет слов «46 „А“» и нет фразы, что рабочим она тоже положена: программу узнают по темам. Часы этой программы в речи не названы</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Некритичное, на допуск не влияет</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>Рабочим — программа «Б», в том числе «ОПП». Лишняя «А» допуск сама не снимает. По таблице 2 программу «А» проходят руководитель ДО и заместители с обязанностями по охране труда, руководители филиалов и их заместители, руководители структурных подразделений и иные руководители с работниками в подчинении. Строка «работники рабочих профессий» программу «А» не содержит</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Рабочим — программа «Б», в том числе «ОПП». Лишняя «А» допуск сама не снимает</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>М-16.01.10-14, раздел 6.5, таблица 2. ПП РФ № 2464, пункт 53 «а» и «б» (программа «а» — руководителям), пункт 53 «д» (рабочие профессии — программа «б»)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="150" customHeight="1">
-      <c r="A6" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>«Программа про безопасные методы и приемы, дистанционный курс. Сидел вечерами по часу в день, уложился за три дня. Тест сдал. Практики не было: только экран и вопросы»</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>3 часа вместо 16 и нет практического блока. Для слесаря программа «Б» обязательна, в таком объёме она недействительна. Дистанционная форма отдельной программы «Б» сама по себе не брак. «По часу в день, три дня» — это три часа, не восемь</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>3 часа вместо 16 и нет практического блока. Дистанционная форма отдельной программы «Б» сама по себе не брак. «По часу в день, три дня» — это три часа, не восемь</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Основание для недопуска</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>16 часов: 12 теории и 4 практики на Портале знаний. Четыре часа — это 25 процентов. Раздел 6.2 запрещает дистанционные технологии для практики программ «В», «ОПП» и «СИЗ», но не для практики отдельной программы «Б». Трёхчасовой курс без практического блока этим требованиям не отвечает. Пункт 66 Правил в редакции от 30.06.2026 № 805 запрещает дистанционно практику первой помощи, практику по СИЗ и занятия на полигонах и тренажёрах. Портальную практику отдельной программы «Б» этот запрет не закрывает, и стандарт её прямо задаёт. Бракуют часы и отсутствие практики, а не слово «дистанционно» и не то, что сидел вечерами</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>16 часов: 12 теории и 4 практики на Портале знаний. Пункт 66 запрещает дистанционно практику первой помощи, практику по СИЗ и занятия на полигонах и тренажёрах. Портальную практику отдельной программы «Б» этот запрет не закрывает. Бракуют часы и отсутствие практики, а не слово «дистанционно» и не то, что сидел вечерами</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>М-16.01.10-14, таблица 1 раздела 6.2, раздел 6.2, раздел 6.5, таблица 2, раздел 6.1, раздел 4. ПП РФ № 2464, пункт 46 «б», пункт 49, пункт 53 «д», пункт 66</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="130" customHeight="1">
-      <c r="A7" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>«В курсе был блок про радиационную безопасность и биологический фактор. На ремонте оборудования такого нет»</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>В программу «Б» включены темы, которые не относятся к трудовой функции слесаря по ремонту технологического оборудования. Это несоответствие содержания. Само по себе допуск не снимает</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
+    <row r="8" ht="102" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>«В курсе «Б» был блок про радиационную безопасность и биологический фактор. На ремонте оборудования такого нет»</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Темы не относятся к работе слесаря по ремонту. Это несоответствие содержания. Само по себе допуск не снимает</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Некритичное, на допуск не влияет</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Программу «Б» собирают по опасностям его работ, по СОУТ и оценке профессиональных рисков, и по шаблону Ш-16.01.10-06. Работы с радиоактивными веществами и источниками ионизирующих излучений — отдельная программа «В» (приложение 1, шаблон Ш-16.01.10-22). Слесарю её не назначают, если он такие работы не выполняет. Отдельный шаблон по биологическому фактору в проверенной карточке не найден, номер не придумываю: тема лишняя по тому же основанию, программа учитывает трудовые функции. Лишние темы не заменяют недостающий объём программы «Б»</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>М-16.01.10-14, раздел 6.1, раздел 6.2, приложение 1. ПП РФ № 2464, пункт 46 «б», пункт 49 (программа учитывает трудовые функции)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="110" customHeight="1">
-      <c r="A8" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Программу «Б» собирают по опасностям его работ. Радиация — отдельная программа «В» (приложение 1, шаблон Ш-16.01.10-22), если он такие работы не выполняет. Отдельный шаблон по биологическому фактору в проверенной карточке не найден, номер не придумываю</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, раздел 6.1, раздел 6.2, приложение 1. ПП РФ № 2464, пункт 46 «б», пункт 49</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="84" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>«С высотой отправили в учебный центр. Полигон, страховочные системы, два дня, экзамен. Протокол и удостоверение обещали вместе». Фразы «только учебный центр, внутри учить нельзя» в речи нет</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Обучение подано в таблице решения так, будто внутри организации оно недопустимо. В речи этого нет. Полигон, СИЗ, два дня и экзамен нарушением не являются</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Некритичное, на допуск не влияет</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Программу «В» по высоте рабочим можно провести внутри. Внешний учебный центр тоже допускается. Два дня на полигоне короче нормы не делают: по таблице 1 программа «В» по высоте — 8 часов, из них 4 часа практики очно</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, раздел 6.1, раздел 6.5, таблица 2, таблица 1 раздела 6.2. ПП РФ № 2464, пункт 44, пункт 55, пункт 99</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="66" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>«Первая помощь — два часа у тренажёра, сердечно-лёгочная реанимация»</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>2 часа вместо 8, практика не выдержана. Отдельная программа «ОПП» — 8 часов, из них 4 часа практики очно, то есть не менее 50 процентов. Двухчасовое занятие этот объём не закрывает. Обучение первой помощи в таком виде недействительно</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>2 часа вместо 8, практика не выдержана</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Основание для недопуска</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>Программа «ОПП»: 8 часов, из них 4 часа практики очно. По таблице 1 теория 4 часа дистанционно, практика 4 часа очно. Практику по первой помощи дистанционно не проводят. Слесарю первая помощь обязательна и как работнику рабочей профессии, и как работнику на высоте. Без действительного обучения к самостоятельной работе не допускают</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Программа «ОПП»: 8 часов, из них 4 часа практики очно</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>М-16.01.10-14, таблица 1 раздела 6.2, раздел 6.2, раздел 6.5, таблица 2, раздел 4. ПП РФ № 2464, пункт 33 «б», пункт 36, пункт 66</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="110" customHeight="1">
-      <c r="A9" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
+    <row r="11" ht="66" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>«В группе 30 человек у одного манекена»</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>При такой организации каждый не отрабатывает навык. С этим совпадает то, что сам Кожевников тренажёр не реанимировал. Числового лимита группы стандарт и № 2464 не задают</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>При такой организации каждый не отрабатывает навык. Числового лимита группы стандарт и № 2464 не задают</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Некритичное, на допуск не влияет</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>Навык должен получить каждый. Жёсткого лимита «не более N человек» в тексте нет, выдуманную цифру не применяем. Практика первой помощи должна дать каждому навык на тренажёре: 4 часа очно внутри программы не короче 8 часов. Неподтверждённая реанимация блокирует допуск строкой 8, а не численность сама по себе</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Навык должен получить каждый. Неподтверждённая реанимация блокирует допуск строкой 10, а не численность сама по себе</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>М-16.01.10-14, раздел 6.2, таблица 1. ПП РФ № 2464, пункт 36. Пункта о предельной численности группы нет</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="100" customHeight="1">
-      <c r="A10" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>«Тренажёр не ожил, тест сдал, протокол подписал, оценка положительная»</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>Навык сердечно-лёгочной реанимации не выполнен, протокол подписан по тесту. Проверка по первой помощи включает умения и навыки. Протокол недостоверен</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
+    <row r="12" ht="66" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>«Тренажёр не ожил, тест сдал, протокол подписал, оценку поставили положительную»</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Навык сердечно-лёгочной реанимации не выполнен, протокол подписан по тесту</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>Основание для недопуска</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
-          <t>Проверка по первой помощи включает умения и навыки, не только тест. Проверка по программе «ОПП» — это проверка знаний, умений и навыков. Невыполненный навык нельзя закрыть оценкой за тест. Без достоверной проверки знания работника к работе не допускают</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>Проверка по первой помощи включает умения и навыки, не только тест</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>М-16.01.10-14, раздел 6.6, раздел 4. ПП РФ № 2464, пункт 37</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="130" customHeight="1">
-      <c r="A11" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>«На Госуслуги пришло уведомление, значит, допущен и все свои работы выполняю»</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>Уведомление принято за допуск. Сама регистрация в реестре нарушением не является. В речи одно уведомление: «проверку знаний прошёл». Про уведомление о других обучениях ничего не сказано</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
+    <row r="13" ht="138" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>«На Госуслуги пришло уведомление: проверку знаний прошёл. Значит, допущен и все свои работы выполняю»</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Уведомление принято за допуск. Сама регистрация в реестре нарушением не является. В речи одно уведомление. Про уведомление о других обучениях ничего не сказано</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>Основание для недопуска</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>Допуск к самостоятельной работе — после инструктажей с проверкой знания, обучения по всем программам своей категории в нужном объёме и стажировки, которая начинается уже после этого обучения. Запись в реестре подтверждает переданные сведения о проверке знания, а не закрывает пробелы. Обратить внимание: про уведомление о других обучениях ничего не сказано. Отдельного пункта Правил про уведомление на Госуслугах нет: уведомление не бракуем и номер ему не придумываем</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>Обратить внимание: про уведомление о других обучениях ничего не сказано. Допуск к самостоятельной работе — после инструктажей с проверкой знания, обучения по программам своей категории и стажировки после этого обучения. Запись в реестре пробелы не закрывает. Отдельного пункта Правил про уведомление на Госуслугах нет, номер не придумываю</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>М-16.01.10-14, раздел 4, раздел 6.1, раздел 6.8. ПП РФ № 2464, пункт 118. Пункта про уведомление на Госуслугах в Правилах нет</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="78" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>Подсказка тренеру. Сначала слушаем речь или смотрим видео. Группа сама делит услышанное на «недопуск» и «некритичное». Карточку открывают после попытки и сверяют список. Красная заливка — основание для недопуска. Жёлтая — некритичное, на допуск не влияет. В таблицу не входят: повтор вводного после ООО «Спецремонт» (раздел 5.2 разрешает повтор в течение года при смене подрядной организации); учебный центр, полигон, два дня и экзамен по высоте; «сидел вечерами» как «не в рабочее время» (в проверенной карточке пункта нет, номер не придумываем); быт — скука, характер преподавателя, шутки старшего мастера. На разборе спросите, почему это отбросили.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="n"/>
-      <c r="B13" s="20" t="n"/>
-      <c r="C13" s="20" t="n"/>
-      <c r="D13" s="20" t="n"/>
-      <c r="E13" s="20" t="n"/>
-      <c r="F13" s="20" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="n"/>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="20" t="n"/>
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>«Проходил обучение на высоте два раза: один раз по правилам по охране труда, присвоили первую группу, второй раз — по новому постановлению Правительства, с номером в государственной системе»</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Дважды прохождение обучения на высоте. Двойная трата бюджета</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Некритичное, на допуск не влияет</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Одно обучение на высоте с присвоением группы и рег.номера. Отдельного пункта, который запрещает второе обучение, в проверенной карточке нет, номер не придумываю. Опора — раздел 6.2: одно обучение учитывает и постановление № 2464, и правила по охране труда; оформляют и протокол, и удостоверение, группу указывают в обоих</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>М-16.01.10-14, раздел 6.2, таблица 1 раздела 6.2, раздел 6.1, раздел 6.5, таблица 2, раздел 6.8. ПП РФ № 2464, пункт 44, пункт 55, пункт 99</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="96" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Сначала слушаем речь или смотрим видео. Группа сама делит услышанное на «недопуск» и «некритичное». Карточку открывают после попытки и сверяют список. Свои находки сверх карточки в ход спора не добавлять: лишнее вынести в «парк вопросов». Красная заливка на печатной карточке — основание для недопуска. Жёлтая — на допуск не влияет. Бытовой шум в таблицу не входит. На разборе можно спросить группу, почему отбросили скуку, характер преподавателя и шутки. Туда же — повтор вводного после «Спецремонта», если его принесли как недопуск, учебный центр по высоте и вечерние занятия, если их принесли как отдельное нарушение.</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="18" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F13"/>
+  <autoFilter ref="A2:F14"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;LЗадание 1. Карточка несоответствий. Только для тренера</oddHeader>
+    <oddHeader>&amp;L&amp;"Calibri"&amp;11 Задание 1. Карточка несоответствий. Только для тренера</oddHeader>
     <oddFooter>&amp;RСтр. &amp;P</oddFooter>
     <evenHeader/>
     <evenFooter/>
